--- a/dataset/01.w_Defects/st_overflow.xlsx
+++ b/dataset/01.w_Defects/st_overflow.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>typedef struct { #if 1 /* Prevent failure? Correspondence */ char buf[524288]; /* 512 Kbytes */ char buf1[131072]; /* 128 Kbytes */ char buf2[131072]; /* 128 Kbytes */ char buf3[1024]; char buf4[1024]; #else /* Prevent failure? Correspondence */ char buf[1024]; #endif /* Prevent failure? Correspondence */ } st_overflow_007_s_001; extern volatile int vflag; void st_overflow_007 () { st_overflow_007_s_001 s; /* 6 Kbytes */ int flag = 10; if (flag) { st_overflow_007_func_001(s); /* 6 Kbytes */ } else { st_overflow_007_func_002(s); /* 6 Kbytes */ } } void st_overflow_007_func_001 (st_overflow_007_s_001 s) { char buf[262144]; /* 256 Kbytes */ s.buf[0] = 1; buf[0] = 1; st_overflow_007_func_002(s); sink = buf[idx]; } void st_overflow_007_func_002 (st_overflow_007_s_001 s) { char buf[262144]; /* 256 Kbytes */ buf[0] = 1; s.buf[0] = 1;/*Tool should detect this line as error*/ /*ERROR:Stack overflow*/ sink = buf[idx]; }</t>
+          <t>typedef struct { #if 1 /* Prevent failure? Correspondence */ char buf[524288]; /* 512 Kbytes */ char buf1[131072]; /* 128 Kbytes */ char buf2[131072]; /* 128 Kbytes */ char buf3[1024]; char buf4[1024]; #else /* Prevent failure? Correspondence */ char buf[1024]; #endif /* Prevent failure? Correspondence */ } st_overflow_007_s_001; extern volatile int vflag; void st_overflow_007 () { st_overflow_007_s_001 s; /* 6 Kbytes */ int flag = 10; if (flag) { st_overflow_007_func_001(s); /* 6 Kbytes */ } else { st_overflow_007_func_002(s); /* 6 Kbytes */ } } void st_overflow_007_func_002 (st_overflow_007_s_001 s) { char buf[262144]; /* 256 Kbytes */ buf[0] = 1; s.buf[0] = 1;/*Tool should detect this line as error*/ /*ERROR:Stack overflow*/ sink = buf[idx]; } void st_overflow_007_func_001 (st_overflow_007_s_001 s) { char buf[262144]; /* 256 Kbytes */ s.buf[0] = 1; buf[0] = 1; st_overflow_007_func_002(s); sink = buf[idx]; }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
